--- a/artfynd/A 40603-2022 artfynd.xlsx
+++ b/artfynd/A 40603-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40603-2022 artfynd.xlsx
+++ b/artfynd/A 40603-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2819,54 +2819,62 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104965553</v>
+        <v>104758348</v>
       </c>
       <c r="B20" t="n">
-        <v>103265</v>
+        <v>98197</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Krokviken, Alnön, Mpd</t>
+          <t>Hästberget, Alnö, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>628737.8221514308</v>
+        <v>628877</v>
       </c>
       <c r="R20" t="n">
-        <v>6916785.853282914</v>
+        <v>6916880</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2891,24 +2899,24 @@
           <t>Alnö</t>
         </is>
       </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Y-Sun-0412</t>
+        </is>
+      </c>
       <c r="Y20" t="inlineStr">
         <is>
           <t>2022-10-09</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-10-09</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>minst 8 dellokaler inom 100 m radie:1587126, 6917562; 1587203, 6917646; 1587272, 6917662;  1587257, 6917718; 1587267, 6917756; 1587084, 6917556 1587249, 6917736</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2921,25 +2929,39 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Äldre naturskog med gran, tall, sälg, björk.</t>
+        </is>
+      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Agneta Toomingas, Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>104965480</v>
+        <v>104965553</v>
       </c>
       <c r="B21" t="n">
-        <v>77506</v>
+        <v>103265</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2948,30 +2970,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2979,10 +3002,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628660.1545271165</v>
+        <v>628737.8221514308</v>
       </c>
       <c r="R21" t="n">
-        <v>6916953.874850863</v>
+        <v>6916785.853282914</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3052,10 +3075,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104965534</v>
+        <v>104965480</v>
       </c>
       <c r="B22" t="n">
-        <v>89412</v>
+        <v>77506</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3068,21 +3091,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3095,10 +3118,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628688.3340262132</v>
+        <v>628660.1545271165</v>
       </c>
       <c r="R22" t="n">
-        <v>6916838.31990282</v>
+        <v>6916953.874850863</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3165,6 +3188,122 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>104965534</v>
+      </c>
+      <c r="B23" t="n">
+        <v>89412</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Krokviken, Alnön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>628688.3340262132</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6916838.31990282</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-10-09</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-10-09</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40603-2022 artfynd.xlsx
+++ b/artfynd/A 40603-2022 artfynd.xlsx
@@ -2822,7 +2822,7 @@
         <v>104758348</v>
       </c>
       <c r="B20" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 40603-2022 artfynd.xlsx
+++ b/artfynd/A 40603-2022 artfynd.xlsx
@@ -2822,7 +2822,7 @@
         <v>104758348</v>
       </c>
       <c r="B20" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2836,11 +2836,6 @@
       </c>
       <c r="E20" t="n">
         <v>220787</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>

--- a/artfynd/A 40603-2022 artfynd.xlsx
+++ b/artfynd/A 40603-2022 artfynd.xlsx
@@ -2822,7 +2822,7 @@
         <v>104758348</v>
       </c>
       <c r="B20" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2836,6 +2836,11 @@
       </c>
       <c r="E20" t="n">
         <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>

--- a/artfynd/A 40603-2022 artfynd.xlsx
+++ b/artfynd/A 40603-2022 artfynd.xlsx
@@ -2822,7 +2822,7 @@
         <v>104758348</v>
       </c>
       <c r="B20" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 40603-2022 artfynd.xlsx
+++ b/artfynd/A 40603-2022 artfynd.xlsx
@@ -2822,7 +2822,7 @@
         <v>104758348</v>
       </c>
       <c r="B20" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 40603-2022 artfynd.xlsx
+++ b/artfynd/A 40603-2022 artfynd.xlsx
@@ -2822,7 +2822,7 @@
         <v>104758348</v>
       </c>
       <c r="B20" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 40603-2022 artfynd.xlsx
+++ b/artfynd/A 40603-2022 artfynd.xlsx
@@ -2822,7 +2822,7 @@
         <v>104758348</v>
       </c>
       <c r="B20" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Y-Sun-0412</t>
+          <t>Y-Sun-0303</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">

--- a/artfynd/A 40603-2022 artfynd.xlsx
+++ b/artfynd/A 40603-2022 artfynd.xlsx
@@ -2822,7 +2822,7 @@
         <v>104758348</v>
       </c>
       <c r="B20" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 40603-2022 artfynd.xlsx
+++ b/artfynd/A 40603-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2819,62 +2819,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104758348</v>
+        <v>104965553</v>
       </c>
       <c r="B20" t="n">
-        <v>98355</v>
+        <v>103265</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hästberget, Alnö, Mpd</t>
+          <t>Krokviken, Alnön, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>628877</v>
+        <v>628737.8221514308</v>
       </c>
       <c r="R20" t="n">
-        <v>6916880</v>
+        <v>6916785.853282914</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2899,24 +2891,24 @@
           <t>Alnö</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>Y-Sun-0303</t>
-        </is>
-      </c>
       <c r="Y20" t="inlineStr">
         <is>
           <t>2022-10-09</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-10-09</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>minst 8 dellokaler inom 100 m radie:1587126, 6917562; 1587203, 6917646; 1587272, 6917662;  1587257, 6917718; 1587267, 6917756; 1587084, 6917556 1587249, 6917736</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2929,39 +2921,25 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Äldre naturskog med gran, tall, sälg, björk.</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Agneta Toomingas, Maria Danvind</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>104965553</v>
+        <v>104965480</v>
       </c>
       <c r="B21" t="n">
-        <v>103265</v>
+        <v>77506</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2970,31 +2948,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3002,10 +2979,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628737.8221514308</v>
+        <v>628660.1545271165</v>
       </c>
       <c r="R21" t="n">
-        <v>6916785.853282914</v>
+        <v>6916953.874850863</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3075,10 +3052,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104965480</v>
+        <v>104965534</v>
       </c>
       <c r="B22" t="n">
-        <v>77506</v>
+        <v>89412</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3091,21 +3068,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3118,10 +3095,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628660.1545271165</v>
+        <v>628688.3340262132</v>
       </c>
       <c r="R22" t="n">
-        <v>6916953.874850863</v>
+        <v>6916838.31990282</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3188,122 +3165,6 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>104965534</v>
-      </c>
-      <c r="B23" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Porodaedalea pini</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Krokviken, Alnön, Mpd</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>628688.3340262132</v>
-      </c>
-      <c r="R23" t="n">
-        <v>6916838.31990282</v>
-      </c>
-      <c r="S23" t="n">
-        <v>25</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Sundsvall</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Alnö</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Maria Danvind</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Maria Danvind</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40603-2022 artfynd.xlsx
+++ b/artfynd/A 40603-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3166,6 +3166,341 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128055011</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98493</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hästberget, Hästberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>628712</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6916796</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128057520</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92623</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Torptjärnen, Torptjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>628801</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6917007</v>
+      </c>
+      <c r="S24" t="n">
+        <v>45</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128057684</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92623</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Torptjärnen, Torptjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>628879</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6916940</v>
+      </c>
+      <c r="S25" t="n">
+        <v>33</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40603-2022 artfynd.xlsx
+++ b/artfynd/A 40603-2022 artfynd.xlsx
@@ -3171,7 +3171,7 @@
         <v>128055011</v>
       </c>
       <c r="B23" t="n">
-        <v>98493</v>
+        <v>98501</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>128057520</v>
       </c>
       <c r="B24" t="n">
-        <v>92623</v>
+        <v>92631</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>128057684</v>
       </c>
       <c r="B25" t="n">
-        <v>92623</v>
+        <v>92631</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 40603-2022 artfynd.xlsx
+++ b/artfynd/A 40603-2022 artfynd.xlsx
@@ -3171,7 +3171,7 @@
         <v>128055011</v>
       </c>
       <c r="B23" t="n">
-        <v>98501</v>
+        <v>98502</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>128057520</v>
       </c>
       <c r="B24" t="n">
-        <v>92631</v>
+        <v>92632</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>128057684</v>
       </c>
       <c r="B25" t="n">
-        <v>92631</v>
+        <v>92632</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 40603-2022 artfynd.xlsx
+++ b/artfynd/A 40603-2022 artfynd.xlsx
@@ -3171,7 +3171,7 @@
         <v>128055011</v>
       </c>
       <c r="B23" t="n">
-        <v>98502</v>
+        <v>98503</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>128057520</v>
       </c>
       <c r="B24" t="n">
-        <v>92632</v>
+        <v>92633</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>128057684</v>
       </c>
       <c r="B25" t="n">
-        <v>92632</v>
+        <v>92633</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 40603-2022 artfynd.xlsx
+++ b/artfynd/A 40603-2022 artfynd.xlsx
@@ -3171,7 +3171,7 @@
         <v>128055011</v>
       </c>
       <c r="B23" t="n">
-        <v>98503</v>
+        <v>98504</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>128057520</v>
       </c>
       <c r="B24" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>128057684</v>
       </c>
       <c r="B25" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 40603-2022 artfynd.xlsx
+++ b/artfynd/A 40603-2022 artfynd.xlsx
@@ -3171,7 +3171,7 @@
         <v>128055011</v>
       </c>
       <c r="B23" t="n">
-        <v>98504</v>
+        <v>98512</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>128057520</v>
       </c>
       <c r="B24" t="n">
-        <v>92634</v>
+        <v>92642</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>128057684</v>
       </c>
       <c r="B25" t="n">
-        <v>92634</v>
+        <v>92642</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 40603-2022 artfynd.xlsx
+++ b/artfynd/A 40603-2022 artfynd.xlsx
@@ -3171,7 +3171,7 @@
         <v>128055011</v>
       </c>
       <c r="B23" t="n">
-        <v>98512</v>
+        <v>98605</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>128057520</v>
       </c>
       <c r="B24" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>128057684</v>
       </c>
       <c r="B25" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 40603-2022 artfynd.xlsx
+++ b/artfynd/A 40603-2022 artfynd.xlsx
@@ -3171,7 +3171,7 @@
         <v>128055011</v>
       </c>
       <c r="B23" t="n">
-        <v>98605</v>
+        <v>98619</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>128057520</v>
       </c>
       <c r="B24" t="n">
-        <v>92734</v>
+        <v>92746</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>128057684</v>
       </c>
       <c r="B25" t="n">
-        <v>92734</v>
+        <v>92746</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 40603-2022 artfynd.xlsx
+++ b/artfynd/A 40603-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>103732282</v>
       </c>
       <c r="B2" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628821.3432513147</v>
+        <v>628821</v>
       </c>
       <c r="R2" t="n">
-        <v>6916985.637225158</v>
+        <v>6916986</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,19 +746,9 @@
           <t>2022-09-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,64 +776,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103999556</v>
+        <v>103997594</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hästberget, Krokviken, Sundsvall, Mpd</t>
+          <t>Hästberget, Sundsvall, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628818.0544634765</v>
+        <v>628881</v>
       </c>
       <c r="R3" t="n">
-        <v>6916853.536909519</v>
+        <v>6916965</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -878,19 +845,9 @@
           <t>2022-10-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,63 +874,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103998952</v>
+        <v>104197595</v>
       </c>
       <c r="B4" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hästberget, Sundsvall, Mpd</t>
+          <t>Krokviken Alnön, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628864.0400864945</v>
+        <v>628867</v>
       </c>
       <c r="R4" t="n">
-        <v>6916928.266254253</v>
+        <v>6916870</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,19 +942,9 @@
           <t>2022-10-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,75 +959,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103997475</v>
+        <v>128057520</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hästberget, Sundsvall, Mpd</t>
+          <t>Torptjärnen, Torptjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628871.099670332</v>
+        <v>628801</v>
       </c>
       <c r="R5" t="n">
-        <v>6916926.214780027</v>
+        <v>6917007</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,22 +1036,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,66 +1066,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Anna Nordbäck</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Anna Nordbäck</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103997594</v>
+        <v>128057684</v>
       </c>
       <c r="B6" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1205</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hästberget, Sundsvall, Mpd</t>
+          <t>Torptjärnen, Torptjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628880.7858264877</v>
+        <v>628879</v>
       </c>
       <c r="R6" t="n">
-        <v>6916964.6928412</v>
+        <v>6916940</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1232,22 +1143,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,72 +1173,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Anna Nordbäck</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Anna Nordbäck</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103996341</v>
+        <v>104965534</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hästberget, Krokviken, Sundsvall, Mpd</t>
+          <t>Krokviken, Alnön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>628886.7389185664</v>
+        <v>628689</v>
       </c>
       <c r="R7" t="n">
-        <v>6916870.588751102</v>
+        <v>6916838</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1357,54 +1256,40 @@
           <t>2022-10-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-09</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103998159</v>
+        <v>104197604</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,47 +1297,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hästberget, Sundsvall, Mpd</t>
+          <t>Krokviken Alnön, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628880.7858264877</v>
+        <v>628843</v>
       </c>
       <c r="R8" t="n">
-        <v>6916964.6928412</v>
+        <v>6916890</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1479,19 +1354,9 @@
           <t>2022-10-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,63 +1371,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103995367</v>
+        <v>104965480</v>
       </c>
       <c r="B9" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Krokviken, Sundsvall, Mpd</t>
+          <t>Krokviken, Alnön, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628876.2659881492</v>
+        <v>628660</v>
       </c>
       <c r="R9" t="n">
-        <v>6916840.444046209</v>
+        <v>6916954</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1592,102 +1454,78 @@
           <t>2022-10-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-10-09</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103996917</v>
+        <v>104197594</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hästberget, Krokviken, Sundsvall, Mpd</t>
+          <t>Krokviken Alnön, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628877.0518245578</v>
+        <v>628882</v>
       </c>
       <c r="R10" t="n">
-        <v>6916880.438938049</v>
+        <v>6916956</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1714,19 +1552,9 @@
           <t>2022-10-09</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1741,27 +1569,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104001503</v>
+        <v>128055011</v>
       </c>
       <c r="B11" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1769,26 +1592,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>219874</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1798,22 +1621,22 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hästberget, Krokviken, Sundsvall, Mpd</t>
+          <t>Hästberget, Hästberget, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628717.1245540036</v>
+        <v>628712</v>
       </c>
       <c r="R11" t="n">
-        <v>6916767.397571614</v>
+        <v>6916796</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1837,22 +1660,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1867,72 +1690,73 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Anna Nordbäck</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Anna Nordbäck</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104001415</v>
+        <v>103733699</v>
       </c>
       <c r="B12" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Krokviken, Sundsvall, Mpd</t>
+          <t>Hästberget, Alnö, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>628710.3321405646</v>
+        <v>628742</v>
       </c>
       <c r="R12" t="n">
-        <v>6916750.406385528</v>
+        <v>6916769</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1959,7 +1783,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2022-09-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -1969,7 +1793,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2022-09-24</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -1983,6 +1807,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2001,15 +1826,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104197599</v>
+        <v>103996341</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,34 +1856,28 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Krokviken Alnön, Mpd</t>
+          <t>Hästberget, Krokviken, Sundsvall, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>628700.5738417748</v>
+        <v>628887</v>
       </c>
       <c r="R13" t="n">
-        <v>6916762.113543859</v>
+        <v>6916871</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2090,93 +1904,87 @@
           <t>2022-10-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-10-09</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104197589</v>
+        <v>103996917</v>
       </c>
       <c r="B14" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221235</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Krokviken Alnön, Mpd</t>
+          <t>Hästberget, Krokviken, Sundsvall, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628892.1191474427</v>
+        <v>628877</v>
       </c>
       <c r="R14" t="n">
-        <v>6916839.660797833</v>
+        <v>6916881</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2203,19 +2011,9 @@
           <t>2022-10-09</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2230,65 +2028,70 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104197587</v>
+        <v>103997475</v>
       </c>
       <c r="B15" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221235</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Krokviken Alnön, Mpd</t>
+          <t>Hästberget, Sundsvall, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628882.1635633274</v>
+        <v>628872</v>
       </c>
       <c r="R15" t="n">
-        <v>6916868.553630653</v>
+        <v>6916926</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2315,19 +2118,9 @@
           <t>2022-10-09</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2342,65 +2135,70 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104197594</v>
+        <v>103998159</v>
       </c>
       <c r="B16" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Krokviken Alnön, Mpd</t>
+          <t>Hästberget, Sundsvall, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628882.0727760294</v>
+        <v>628881</v>
       </c>
       <c r="R16" t="n">
-        <v>6916955.448610782</v>
+        <v>6916965</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2429,7 +2227,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2439,7 +2237,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2454,65 +2252,74 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104197595</v>
+        <v>103999556</v>
       </c>
       <c r="B17" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Krokviken Alnön, Mpd</t>
+          <t>Hästberget, Krokviken, Sundsvall, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628866.7752326778</v>
+        <v>628818</v>
       </c>
       <c r="R17" t="n">
-        <v>6916869.354816287</v>
+        <v>6916854</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2541,7 +2348,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2551,7 +2358,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2566,62 +2373,73 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104197604</v>
+        <v>104197597</v>
       </c>
       <c r="B18" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Krokviken Alnön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628842.7007456026</v>
+        <v>628863</v>
       </c>
       <c r="R18" t="n">
-        <v>6916890.268331735</v>
+        <v>6916944</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2651,27 +2469,18 @@
           <t>2022-10-09</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-10-09</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2690,15 +2499,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104197597</v>
+        <v>104197599</v>
       </c>
       <c r="B19" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2725,7 +2529,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2746,10 +2550,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>628862.9496974708</v>
+        <v>628700</v>
       </c>
       <c r="R19" t="n">
-        <v>6916944.488538592</v>
+        <v>6916762</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2779,19 +2583,9 @@
           <t>2022-10-09</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2819,54 +2613,57 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104965553</v>
+        <v>104758348</v>
       </c>
       <c r="B20" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Krokviken, Alnön, Mpd</t>
+          <t>Hästberget, Alnö, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>628737.8221514308</v>
+        <v>628877</v>
       </c>
       <c r="R20" t="n">
-        <v>6916785.853282914</v>
+        <v>6916880</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2891,24 +2688,24 @@
           <t>Alnö</t>
         </is>
       </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Y-Sun-0303</t>
+        </is>
+      </c>
       <c r="Y20" t="inlineStr">
         <is>
           <t>2022-10-09</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-10-09</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>minst 8 dellokaler inom 100 m radie:1587126, 6917562; 1587203, 6917646; 1587272, 6917662;  1587257, 6917718; 1587267, 6917756; 1587084, 6917556 1587249, 6917736</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2921,68 +2718,84 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Äldre naturskog med gran, tall, sälg, björk.</t>
+        </is>
+      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Agneta Toomingas, Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>104965480</v>
+        <v>103998952</v>
       </c>
       <c r="B21" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Krokviken, Alnön, Mpd</t>
+          <t>Hästberget, Sundsvall, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628660.1545271165</v>
+        <v>628865</v>
       </c>
       <c r="R21" t="n">
-        <v>6916953.874850863</v>
+        <v>6916928</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3012,93 +2825,84 @@
           <t>2022-10-09</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-10-09</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104965534</v>
+        <v>104001415</v>
       </c>
       <c r="B22" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Krokviken, Alnön, Mpd</t>
+          <t>Krokviken, Sundsvall, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628688.3340262132</v>
+        <v>628711</v>
       </c>
       <c r="R22" t="n">
-        <v>6916838.31990282</v>
+        <v>6916750</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3128,50 +2932,39 @@
           <t>2022-10-09</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-10-09</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128055011</v>
+        <v>104001503</v>
       </c>
       <c r="B23" t="n">
-        <v>98619</v>
+        <v>106244</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3179,26 +2972,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219874</v>
+        <v>221144</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3208,22 +3001,22 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hästberget, Hästberget, Mpd</t>
+          <t>Hästberget, Krokviken, Sundsvall, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628712</v>
+        <v>628717</v>
       </c>
       <c r="R23" t="n">
-        <v>6916796</v>
+        <v>6916767</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3247,22 +3040,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:06</t>
+          <t>2022-10-09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:06</t>
+          <t>2022-10-09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3277,60 +3060,64 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anna Nordbäck</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anna Nordbäck</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128057520</v>
+        <v>104965553</v>
       </c>
       <c r="B24" t="n">
-        <v>92746</v>
+        <v>106244</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>221144</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Torptjärnen, Torptjärnen, Mpd</t>
+          <t>Krokviken, Alnön, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>628801</v>
+        <v>628738</v>
       </c>
       <c r="R24" t="n">
-        <v>6917007</v>
+        <v>6916786</v>
       </c>
       <c r="S24" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3354,22 +3141,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:35</t>
+          <t>2022-10-09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:35</t>
+          <t>2022-10-09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3378,28 +3155,29 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna Nordbäck</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna Nordbäck</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128057684</v>
+        <v>104197587</v>
       </c>
       <c r="B25" t="n">
-        <v>92746</v>
+        <v>102241</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3407,37 +3185,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>221235</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Torptjärnen, Torptjärnen, Mpd</t>
+          <t>Krokviken Alnön, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628879</v>
+        <v>628882</v>
       </c>
       <c r="R25" t="n">
-        <v>6916940</v>
+        <v>6916869</v>
       </c>
       <c r="S25" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3461,22 +3239,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:45</t>
+          <t>2022-10-09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:45</t>
+          <t>2022-10-09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3491,15 +3259,210 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna Nordbäck</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna Nordbäck</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>104197589</v>
+      </c>
+      <c r="B26" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Krokviken Alnön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>628892</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6916839</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2022-10-09</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2022-10-09</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>103995367</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Krokviken, Sundsvall, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>628876</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6916840</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2022-10-09</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2022-10-09</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40603-2022 artfynd.xlsx
+++ b/artfynd/A 40603-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103732282</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997594</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104197595</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128057520</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128057684</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104965534</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1380,6 +1415,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104197604</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1481,6 +1521,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104965480</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1578,6 +1623,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104197594</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1699,6 +1749,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128055011</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1825,6 +1880,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134853797</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1936,6 +1996,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135104199</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2060,6 +2125,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103733699</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2167,6 +2237,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103996341</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2274,6 +2349,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103996917</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2381,6 +2461,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997475</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2498,6 +2583,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998159</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2619,6 +2709,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103999556</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2733,6 +2828,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104197597</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2847,6 +2947,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104197599</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2981,6 +3086,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104758348</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3088,6 +3198,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998952</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3195,6 +3310,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104001415</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3306,6 +3426,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104001503</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3408,6 +3533,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104965553</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3519,6 +3649,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135103900</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3616,6 +3751,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104197587</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3713,6 +3853,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104197589</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3811,8 +3956,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995367</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 40603-2022 artfynd.xlsx
+++ b/artfynd/A 40603-2022 artfynd.xlsx
@@ -1891,7 +1891,7 @@
         <v>135104199</v>
       </c>
       <c r="B13" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>135103900</v>
       </c>
       <c r="B27" t="n">
-        <v>106324</v>
+        <v>106379</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 40603-2022 artfynd.xlsx
+++ b/artfynd/A 40603-2022 artfynd.xlsx
@@ -1891,7 +1891,7 @@
         <v>135104199</v>
       </c>
       <c r="B13" t="n">
-        <v>99277</v>
+        <v>99304</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>135103900</v>
       </c>
       <c r="B27" t="n">
-        <v>106379</v>
+        <v>106406</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
